--- a/data/numeric/input/old_data_62/file_1724824061558.xlsx
+++ b/data/numeric/input/old_data_62/file_1724824061558.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29721"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_A8571EF724803F54CEC8541C6E397EC9EEF5E399" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{505676BC-DAC0-4C23-9BDA-AD1106FBC97B}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="11_A8571EF724803F54CEC8541C6E397EC9EEF5E399" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F4F3B786-0EB7-45C5-9B10-C3245A090C4E}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="124">
   <si>
     <t>订单ID</t>
   </si>
@@ -240,9 +240,6 @@
     <t>G区</t>
   </si>
   <si>
-    <t>李玉兰</t>
-  </si>
-  <si>
     <t>取消</t>
   </si>
   <si>
@@ -250,9 +247,6 @@
   </si>
   <si>
     <t>50</t>
-  </si>
-  <si>
-    <t>李成</t>
   </si>
   <si>
     <t>14</t>
@@ -444,8 +438,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1099,8 +1096,8 @@
       <c r="J8" t="s">
         <v>68</v>
       </c>
-      <c r="K8" t="s">
-        <v>69</v>
+      <c r="K8" s="1">
+        <v>9.1</v>
       </c>
       <c r="L8" t="s">
         <v>56</v>
@@ -1109,7 +1106,7 @@
         <v>57</v>
       </c>
       <c r="N8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1120,7 +1117,7 @@
         <v>30</v>
       </c>
       <c r="C9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D9" t="s">
         <v>20</v>
@@ -1135,7 +1132,7 @@
         <v>27</v>
       </c>
       <c r="H9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I9" t="s">
         <v>41</v>
@@ -1143,8 +1140,8 @@
       <c r="J9" t="s">
         <v>62</v>
       </c>
-      <c r="K9" t="s">
-        <v>73</v>
+      <c r="K9" s="1">
+        <v>13</v>
       </c>
       <c r="L9" t="s">
         <v>17</v>
@@ -1158,13 +1155,13 @@
     </row>
     <row r="10" spans="1:18">
       <c r="A10" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B10" t="s">
         <v>65</v>
       </c>
       <c r="C10" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D10" t="s">
         <v>20</v>
@@ -1179,22 +1176,22 @@
         <v>22</v>
       </c>
       <c r="H10" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="I10" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="J10" t="s">
         <v>24</v>
       </c>
       <c r="K10" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="L10" t="s">
         <v>17</v>
       </c>
       <c r="M10" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="N10" t="s">
         <v>29</v>
@@ -1202,13 +1199,13 @@
     </row>
     <row r="11" spans="1:18">
       <c r="A11" t="s">
+        <v>78</v>
+      </c>
+      <c r="B11" t="s">
+        <v>79</v>
+      </c>
+      <c r="C11" t="s">
         <v>80</v>
-      </c>
-      <c r="B11" t="s">
-        <v>81</v>
-      </c>
-      <c r="C11" t="s">
-        <v>82</v>
       </c>
       <c r="D11" t="s">
         <v>20</v>
@@ -1223,7 +1220,7 @@
         <v>22</v>
       </c>
       <c r="H11" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="I11" t="s">
         <v>53</v>
@@ -1232,7 +1229,7 @@
         <v>54</v>
       </c>
       <c r="K11" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="L11" t="s">
         <v>17</v>
@@ -1246,13 +1243,13 @@
     </row>
     <row r="12" spans="1:18">
       <c r="A12" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B12" t="s">
         <v>18</v>
       </c>
       <c r="C12" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D12" t="s">
         <v>20</v>
@@ -1267,7 +1264,7 @@
         <v>22</v>
       </c>
       <c r="H12" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="I12" t="s">
         <v>41</v>
@@ -1276,10 +1273,10 @@
         <v>62</v>
       </c>
       <c r="K12" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="L12" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="M12" t="s">
         <v>49</v>
@@ -1290,13 +1287,13 @@
     </row>
     <row r="13" spans="1:18">
       <c r="A13" t="s">
+        <v>87</v>
+      </c>
+      <c r="B13" t="s">
+        <v>88</v>
+      </c>
+      <c r="C13" t="s">
         <v>89</v>
-      </c>
-      <c r="B13" t="s">
-        <v>90</v>
-      </c>
-      <c r="C13" t="s">
-        <v>91</v>
       </c>
       <c r="D13" t="s">
         <v>20</v>
@@ -1311,7 +1308,7 @@
         <v>36</v>
       </c>
       <c r="H13" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I13" t="s">
         <v>41</v>
@@ -1320,10 +1317,10 @@
         <v>54</v>
       </c>
       <c r="K13" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="L13" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="M13" t="s">
         <v>49</v>
@@ -1334,13 +1331,13 @@
     </row>
     <row r="14" spans="1:18">
       <c r="A14" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B14" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C14" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D14" t="s">
         <v>20</v>
@@ -1355,19 +1352,19 @@
         <v>27</v>
       </c>
       <c r="H14" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="I14" t="s">
         <v>68</v>
       </c>
       <c r="J14" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="K14" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="L14" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="M14" t="s">
         <v>57</v>
@@ -1378,13 +1375,13 @@
     </row>
     <row r="15" spans="1:18">
       <c r="A15" t="s">
+        <v>95</v>
+      </c>
+      <c r="B15" t="s">
+        <v>96</v>
+      </c>
+      <c r="C15" t="s">
         <v>97</v>
-      </c>
-      <c r="B15" t="s">
-        <v>98</v>
-      </c>
-      <c r="C15" t="s">
-        <v>99</v>
       </c>
       <c r="D15" t="s">
         <v>32</v>
@@ -1393,22 +1390,22 @@
         <v>20</v>
       </c>
       <c r="F15" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G15" t="s">
         <v>22</v>
       </c>
       <c r="H15" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="I15" t="s">
         <v>68</v>
       </c>
       <c r="J15" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="K15" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="L15" t="s">
         <v>55</v>
@@ -1422,13 +1419,13 @@
     </row>
     <row r="16" spans="1:18">
       <c r="A16" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B16" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C16" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D16" t="s">
         <v>20</v>
@@ -1443,7 +1440,7 @@
         <v>27</v>
       </c>
       <c r="H16" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="I16" t="s">
         <v>62</v>
@@ -1458,7 +1455,7 @@
         <v>55</v>
       </c>
       <c r="M16" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="N16" t="s">
         <v>29</v>
@@ -1466,13 +1463,13 @@
     </row>
     <row r="17" spans="1:14">
       <c r="A17" t="s">
+        <v>105</v>
+      </c>
+      <c r="B17" t="s">
+        <v>106</v>
+      </c>
+      <c r="C17" t="s">
         <v>107</v>
-      </c>
-      <c r="B17" t="s">
-        <v>108</v>
-      </c>
-      <c r="C17" t="s">
-        <v>109</v>
       </c>
       <c r="D17" t="s">
         <v>20</v>
@@ -1487,7 +1484,7 @@
         <v>22</v>
       </c>
       <c r="H17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="I17" t="s">
         <v>25</v>
@@ -1496,7 +1493,7 @@
         <v>54</v>
       </c>
       <c r="K17" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="L17" t="s">
         <v>55</v>
@@ -1513,10 +1510,10 @@
         <v>55</v>
       </c>
       <c r="B18" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C18" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D18" t="s">
         <v>32</v>
@@ -1531,7 +1528,7 @@
         <v>27</v>
       </c>
       <c r="H18" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="I18" t="s">
         <v>53</v>
@@ -1540,27 +1537,27 @@
         <v>54</v>
       </c>
       <c r="K18" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="L18" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="M18" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="N18" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B19" t="s">
         <v>45</v>
       </c>
       <c r="C19" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D19" t="s">
         <v>32</v>
@@ -1575,7 +1572,7 @@
         <v>36</v>
       </c>
       <c r="H19" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I19" t="s">
         <v>62</v>
@@ -1584,10 +1581,10 @@
         <v>53</v>
       </c>
       <c r="K19" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="L19" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="M19" t="s">
         <v>26</v>
@@ -1598,13 +1595,13 @@
     </row>
     <row r="20" spans="1:14">
       <c r="A20" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B20" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C20" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D20" t="s">
         <v>32</v>
@@ -1613,13 +1610,13 @@
         <v>20</v>
       </c>
       <c r="F20" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G20" t="s">
         <v>27</v>
       </c>
       <c r="H20" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I20" t="s">
         <v>24</v>
@@ -1628,13 +1625,13 @@
         <v>62</v>
       </c>
       <c r="K20" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="L20" t="s">
         <v>37</v>
       </c>
       <c r="M20" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="N20" t="s">
         <v>29</v>
@@ -1648,7 +1645,7 @@
         <v>50</v>
       </c>
       <c r="C21" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D21" t="s">
         <v>32</v>
@@ -1657,28 +1654,28 @@
         <v>32</v>
       </c>
       <c r="F21" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G21" t="s">
         <v>36</v>
       </c>
       <c r="H21" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="I21" t="s">
         <v>68</v>
       </c>
       <c r="J21" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="K21" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="L21" t="s">
         <v>58</v>
       </c>
       <c r="M21" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="N21" t="s">
         <v>29</v>
@@ -1690,21 +1687,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="文档" ma:contentTypeID="0x01010028C7B6C620067247A35EF62A3E68EE62" ma:contentTypeVersion="2" ma:contentTypeDescription="新建文档。" ma:contentTypeScope="" ma:versionID="afb9c51b290a08b96651a149e23bf63d">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="eca6eae4-1627-4e8d-9a6b-5b4dd91506e7" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5c256d110dbc588a3a1a6b419ffcea87" ns2:_="">
     <xsd:import namespace="eca6eae4-1627-4e8d-9a6b-5b4dd91506e7"/>
@@ -1852,8 +1834,23 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1F2121C8-9DE1-4B62-A800-2FD6BFBAF822}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC7431B5-A426-440F-AA32-354E5B3A97E3}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1861,5 +1858,5 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC7431B5-A426-440F-AA32-354E5B3A97E3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1F2121C8-9DE1-4B62-A800-2FD6BFBAF822}"/>
 </file>